--- a/eval-runner/orchestrator/results/score_RC2_r1/RC2_코퍼스_큐레이션_작업목록_v1_0.xlsx
+++ b/eval-runner/orchestrator/results/score_RC2_r1/RC2_코퍼스_큐레이션_작업목록_v1_0.xlsx
@@ -462,8 +462,11 @@
           <t>https://www.remotecall.com/kr</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -479,8 +482,11 @@
           <t>https://www.remotecall.com/kr/</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -496,8 +502,11 @@
           <t>https://www.remotecall.com/kr/blog</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -513,8 +522,11 @@
           <t>https://www.remotecall.com/kr/blog/</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -530,8 +542,11 @@
           <t>https://www.remotecall.com/kr/blog/2025-cost-saving-survival/</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -547,8 +562,11 @@
           <t>https://www.remotecall.com/kr/blog/764update-250820/</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -564,8 +582,11 @@
           <t>https://www.remotecall.com/kr/blog/765update-251126/</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -581,8 +602,11 @@
           <t>https://www.remotecall.com/kr/blog/access-page-template/</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -598,8 +622,6 @@
           <t>https://www.remotecall.com/kr/blog/advantage-of-remote-support-solution/</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -615,8 +637,6 @@
           <t>https://www.remotecall.com/kr/blog/against-low-birth-rate/</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -632,8 +652,6 @@
           <t>https://www.remotecall.com/kr/blog/ai-chatbot-limitations-remote-support/</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -649,8 +667,6 @@
           <t>https://www.remotecall.com/kr/blog/ai-chatbot/</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -666,8 +682,11 @@
           <t>https://www.remotecall.com/kr/blog/ces-2025-trend-summary/</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -683,8 +702,11 @@
           <t>https://www.remotecall.com/kr/blog/cloud-voucher-2024/</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -700,8 +722,11 @@
           <t>https://www.remotecall.com/kr/blog/consumption-coupon-2nd/</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -717,8 +742,11 @@
           <t>https://www.remotecall.com/kr/blog/customer-satisfaction/</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -734,8 +762,11 @@
           <t>https://www.remotecall.com/kr/blog/dcompany-choice-remotecall-visualpack/</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -751,8 +782,11 @@
           <t>https://www.remotecall.com/kr/blog/difference-from-low/</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -768,8 +802,11 @@
           <t>https://www.remotecall.com/kr/blog/dx-of-manufacturing-02/</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -785,8 +822,11 @@
           <t>https://www.remotecall.com/kr/blog/dx-of-manufacturing/</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -802,8 +842,11 @@
           <t>https://www.remotecall.com/kr/blog/financial-sector-dx-tip/</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -819,8 +862,11 @@
           <t>https://www.remotecall.com/kr/blog/git-interview-remotecall/</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -836,8 +882,11 @@
           <t>https://www.remotecall.com/kr/blog/government-digital-transformation/</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -853,8 +902,11 @@
           <t>https://www.remotecall.com/kr/blog/governmental-procurement/</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -870,8 +922,11 @@
           <t>https://www.remotecall.com/kr/blog/gpt-4o-discusses-remotecall/</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -887,8 +942,11 @@
           <t>https://www.remotecall.com/kr/blog/gs-certification/</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -904,8 +962,11 @@
           <t>https://www.remotecall.com/kr/blog/holiday-customer-support-remotecall/</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -921,8 +982,11 @@
           <t>https://www.remotecall.com/kr/blog/how-to-add-remote-support-vibe-coding/</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -938,8 +1002,11 @@
           <t>https://www.remotecall.com/kr/blog/importance-of-security/</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -955,8 +1022,11 @@
           <t>https://www.remotecall.com/kr/blog/iso-iec-27001-2022/</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -972,8 +1042,11 @@
           <t>https://www.remotecall.com/kr/blog/iso27001-certification/</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -989,8 +1062,11 @@
           <t>https://www.remotecall.com/kr/blog/it-support-tip/</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1006,8 +1082,11 @@
           <t>https://www.remotecall.com/kr/blog/it-trend/</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1023,8 +1102,11 @@
           <t>https://www.remotecall.com/kr/blog/medical-software-support-solution/</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1040,8 +1122,11 @@
           <t>https://www.remotecall.com/kr/blog/mobile-remote-support/</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1057,8 +1142,11 @@
           <t>https://www.remotecall.com/kr/blog/moving-is-difficult/</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1074,8 +1162,11 @@
           <t>https://www.remotecall.com/kr/blog/new-office-building/</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1091,8 +1182,11 @@
           <t>https://www.remotecall.com/kr/blog/news-kospi5000/</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1108,8 +1202,11 @@
           <t>https://www.remotecall.com/kr/blog/non-face-voucher-guide/</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1125,8 +1222,11 @@
           <t>https://www.remotecall.com/kr/blog/non-face-voucher/</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1142,8 +1242,11 @@
           <t>https://www.remotecall.com/kr/blog/nttdocomoawards-rsupport/</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1159,8 +1262,11 @@
           <t>https://www.remotecall.com/kr/blog/onsite-support/</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1176,8 +1282,11 @@
           <t>https://www.remotecall.com/kr/blog/osstemimplant-adoption-remotecall/</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1193,8 +1302,11 @@
           <t>https://www.remotecall.com/kr/blog/page/2/</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1210,8 +1322,11 @@
           <t>https://www.remotecall.com/kr/blog/page/3/</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1227,8 +1342,11 @@
           <t>https://www.remotecall.com/kr/blog/persuade-remotecall/</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1244,8 +1362,11 @@
           <t>https://www.remotecall.com/kr/blog/phone-release/</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1261,8 +1382,6 @@
           <t>https://www.remotecall.com/kr/blog/rainyseason-damand/</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1278,8 +1397,11 @@
           <t>https://www.remotecall.com/kr/blog/rcvp-for-accident/</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1295,8 +1417,11 @@
           <t>https://www.remotecall.com/kr/blog/remote-support-blinder/</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1312,8 +1437,11 @@
           <t>https://www.remotecall.com/kr/blog/remote-support-tech-solutions/</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1329,8 +1457,11 @@
           <t>https://www.remotecall.com/kr/blog/remotecall-connection-guide/</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1346,8 +1477,11 @@
           <t>https://www.remotecall.com/kr/blog/remotecall-customer-case-initech/</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1363,8 +1497,11 @@
           <t>https://www.remotecall.com/kr/blog/remotecall-for-everyone/</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1380,8 +1517,11 @@
           <t>https://www.remotecall.com/kr/blog/remotecall-it-infra-support/</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1397,8 +1537,6 @@
           <t>https://www.remotecall.com/kr/blog/remotecall-it-kakao/</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1414,8 +1552,11 @@
           <t>https://www.remotecall.com/kr/blog/remotecall-macos-remote-support/</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1431,8 +1572,11 @@
           <t>https://www.remotecall.com/kr/blog/remotecall-maintenance-sbank-case-study/</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1448,8 +1592,11 @@
           <t>https://www.remotecall.com/kr/blog/remotecall-various-support/</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1465,8 +1612,11 @@
           <t>https://www.remotecall.com/kr/blog/remotecall-visualpack-innovation/</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
-      <c r="E61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1482,8 +1632,11 @@
           <t>https://www.remotecall.com/kr/blog/remotecall-webviewer-multi-monitor-remote-support/</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -1499,8 +1652,11 @@
           <t>https://www.remotecall.com/kr/blog/remotecall-wins-2025-global-acx-innovation-award/</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr"/>
-      <c r="E63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1516,8 +1672,11 @@
           <t>https://www.remotecall.com/kr/blog/remotevs-sales/</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr"/>
-      <c r="E64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -1533,8 +1692,11 @@
           <t>https://www.remotecall.com/kr/blog/rsupport-remotecall-iso-27001-27017-certification/</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
-      <c r="E65" t="inlineStr"/>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -1550,8 +1712,11 @@
           <t>https://www.remotecall.com/kr/blog/rsupport-swcc-expo-2025/</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr"/>
-      <c r="E66" t="inlineStr"/>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -1567,8 +1732,11 @@
           <t>https://www.remotecall.com/kr/blog/sdk-update-remotecall/</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr"/>
-      <c r="E67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -1584,8 +1752,11 @@
           <t>https://www.remotecall.com/kr/blog/sharp-cases/</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr"/>
-      <c r="E68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -1601,8 +1772,11 @@
           <t>https://www.remotecall.com/kr/blog/solution-review/</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr"/>
-      <c r="E69" t="inlineStr"/>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -1618,8 +1792,11 @@
           <t>https://www.remotecall.com/kr/blog/tes-remotecall-remote-support/</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr"/>
-      <c r="E70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -1635,8 +1812,11 @@
           <t>https://www.remotecall.com/kr/blog/tes-speed-up-2x/</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr"/>
-      <c r="E71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -1652,8 +1832,11 @@
           <t>https://www.remotecall.com/kr/blog/time-efficient-society/</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr"/>
-      <c r="E72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -1669,8 +1852,11 @@
           <t>https://www.remotecall.com/kr/blog/upgrade-it-remote-support/</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr"/>
-      <c r="E73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -1686,8 +1872,11 @@
           <t>https://www.remotecall.com/kr/blog/visual-support-for-manufacturers/</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr"/>
-      <c r="E74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -1703,8 +1892,11 @@
           <t>https://www.remotecall.com/kr/blog/what-is-remote-support/</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr"/>
-      <c r="E75" t="inlineStr"/>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -1720,8 +1912,11 @@
           <t>https://www.remotecall.com/kr/blog/winner-of-software-company/</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr"/>
-      <c r="E76" t="inlineStr"/>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -1737,8 +1932,11 @@
           <t>https://www.remotecall.com/kr/blog/workcation/</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr"/>
-      <c r="E77" t="inlineStr"/>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -1754,8 +1952,11 @@
           <t>https://www.remotecall.com/kr/contact</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr"/>
-      <c r="E78" t="inlineStr"/>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -1771,8 +1972,11 @@
           <t>https://www.remotecall.com/kr/contact-us/</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr"/>
-      <c r="E79" t="inlineStr"/>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -1788,8 +1992,6 @@
           <t>https://www.remotecall.com/kr/footer/contact-us/</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr"/>
-      <c r="E80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -1805,8 +2007,11 @@
           <t>https://www.remotecall.com/kr/info/library/</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr"/>
-      <c r="E81" t="inlineStr"/>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -1822,8 +2027,11 @@
           <t>https://www.remotecall.com/kr/info/lounge/</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr"/>
-      <c r="E82" t="inlineStr"/>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -1839,8 +2047,11 @@
           <t>https://www.remotecall.com/kr/info/notices/</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr"/>
-      <c r="E83" t="inlineStr"/>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -1856,8 +2067,11 @@
           <t>https://www.remotecall.com/kr/library/choice-for-cost-efficiency/</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr"/>
-      <c r="E84" t="inlineStr"/>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -1873,8 +2087,11 @@
           <t>https://www.remotecall.com/kr/library/control-variable-on-telecommuting/</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr"/>
-      <c r="E85" t="inlineStr"/>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -1890,8 +2107,11 @@
           <t>https://www.remotecall.com/kr/library/importance-of-time-management/</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr"/>
-      <c r="E86" t="inlineStr"/>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -1907,8 +2127,11 @@
           <t>https://www.remotecall.com/kr/library/keep-the-infrastructure/</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr"/>
-      <c r="E87" t="inlineStr"/>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -1924,8 +2147,11 @@
           <t>https://www.remotecall.com/kr/library/remotecall-is-your-cure/</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr"/>
-      <c r="E88" t="inlineStr"/>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -1941,8 +2167,11 @@
           <t>https://www.remotecall.com/kr/library/remotecall-usage-tips/</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr"/>
-      <c r="E89" t="inlineStr"/>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -1958,8 +2187,11 @@
           <t>https://www.remotecall.com/kr/library/start-remotecall-on-internet/</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr"/>
-      <c r="E90" t="inlineStr"/>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -1975,8 +2207,11 @@
           <t>https://www.remotecall.com/kr/library/why-need-mobile-support/</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr"/>
-      <c r="E91" t="inlineStr"/>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -1992,8 +2227,6 @@
           <t>https://www.remotecall.com/kr/notices/promotion/free-remotecall-and-free-coffee/</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr"/>
-      <c r="E92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -2009,8 +2242,11 @@
           <t>https://www.remotecall.com/kr/notices/promotion/salespromotion2024/</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr"/>
-      <c r="E93" t="inlineStr"/>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -2026,8 +2262,11 @@
           <t>https://www.remotecall.com/kr/pricing/</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr"/>
-      <c r="E94" t="inlineStr"/>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -2043,8 +2282,11 @@
           <t>https://www.remotecall.com/kr/pricing/api-sdk/</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr"/>
-      <c r="E95" t="inlineStr"/>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -2060,8 +2302,11 @@
           <t>https://www.remotecall.com/kr/pricing/inquiry/</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr"/>
-      <c r="E96" t="inlineStr"/>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -2077,8 +2322,11 @@
           <t>https://www.remotecall.com/kr/pricing/on-premise/</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr"/>
-      <c r="E97" t="inlineStr"/>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -2094,8 +2342,11 @@
           <t>https://www.remotecall.com/kr/pricing/saas</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr"/>
-      <c r="E98" t="inlineStr"/>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -2111,8 +2362,11 @@
           <t>https://www.remotecall.com/kr/pricing/saas/</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr"/>
-      <c r="E99" t="inlineStr"/>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -2128,8 +2382,11 @@
           <t>https://www.remotecall.com/kr/products/</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr"/>
-      <c r="E100" t="inlineStr"/>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -2145,8 +2402,11 @@
           <t>https://www.remotecall.com/kr/products/advantages/</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr"/>
-      <c r="E101" t="inlineStr"/>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -2162,8 +2422,11 @@
           <t>https://www.remotecall.com/kr/products/ai-assistant/</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr"/>
-      <c r="E102" t="inlineStr"/>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -2179,8 +2442,11 @@
           <t>https://www.remotecall.com/kr/products/features/</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr"/>
-      <c r="E103" t="inlineStr"/>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -2196,8 +2462,11 @@
           <t>https://www.remotecall.com/kr/products/mobile-support-sdk/</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr"/>
-      <c r="E104" t="inlineStr"/>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -2213,8 +2482,11 @@
           <t>https://www.remotecall.com/kr/products/mobile-support/</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr"/>
-      <c r="E105" t="inlineStr"/>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -2230,8 +2502,11 @@
           <t>https://www.remotecall.com/kr/products/non-face-service/</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr"/>
-      <c r="E106" t="inlineStr"/>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -2247,8 +2522,11 @@
           <t>https://www.remotecall.com/kr/products/pc-support/</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr"/>
-      <c r="E107" t="inlineStr"/>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -2264,8 +2542,11 @@
           <t>https://www.remotecall.com/kr/products/remotecall-face/</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr"/>
-      <c r="E108" t="inlineStr"/>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -2281,8 +2562,11 @@
           <t>https://www.remotecall.com/kr/products/remotecall-sdk/</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr"/>
-      <c r="E109" t="inlineStr"/>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -2298,8 +2582,11 @@
           <t>https://www.remotecall.com/kr/products/remotecall/</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr"/>
-      <c r="E110" t="inlineStr"/>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -2315,8 +2602,11 @@
           <t>https://www.remotecall.com/kr/products/requirements/</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr"/>
-      <c r="E111" t="inlineStr"/>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -2332,8 +2622,11 @@
           <t>https://www.remotecall.com/kr/products/visual-support/</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr"/>
-      <c r="E112" t="inlineStr"/>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -2349,8 +2642,11 @@
           <t>https://www.remotecall.com/kr/products/webviewer/</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr"/>
-      <c r="E113" t="inlineStr"/>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -2366,8 +2662,11 @@
           <t>https://www.remotecall.com/kr/purchase/pricing/</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr"/>
-      <c r="E114" t="inlineStr"/>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -2383,8 +2682,11 @@
           <t>https://www.remotecall.com/kr/store/product/?prd=ent</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr"/>
-      <c r="E115" t="inlineStr"/>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -2400,8 +2702,6 @@
           <t>https://www.remotecall.com/kr/store/product/?prd=mpack</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr"/>
-      <c r="E116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -2417,8 +2717,11 @@
           <t>https://www.remotecall.com/kr/store/product/?prd=pro</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr"/>
-      <c r="E117" t="inlineStr"/>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -2434,8 +2737,11 @@
           <t>https://www.remotecall.com/kr/store/product/?prd=vpack</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr"/>
-      <c r="E118" t="inlineStr"/>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -2451,8 +2757,11 @@
           <t>https://www.remotecall.com/kr/success-stories/customer-support/ceragem/</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr"/>
-      <c r="E119" t="inlineStr"/>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -2468,8 +2777,6 @@
           <t>https://www.remotecall.com/kr/success-stories/customer-support/jwonit/</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr"/>
-      <c r="E120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -2485,8 +2792,11 @@
           <t>https://www.remotecall.com/kr/success-stories/customer-support/koiis/</t>
         </is>
       </c>
-      <c r="D121" t="inlineStr"/>
-      <c r="E121" t="inlineStr"/>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -2502,8 +2812,6 @@
           <t>https://www.remotecall.com/kr/success-stories/customer-support/lg-electronics-smartphone/</t>
         </is>
       </c>
-      <c r="D122" t="inlineStr"/>
-      <c r="E122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -2519,8 +2827,6 @@
           <t>https://www.remotecall.com/kr/success-stories/customer-support/woori-bank/</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr"/>
-      <c r="E123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -2536,8 +2842,11 @@
           <t>https://www.remotecall.com/kr/success-stories/internal-support/puritech/</t>
         </is>
       </c>
-      <c r="D124" t="inlineStr"/>
-      <c r="E124" t="inlineStr"/>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -2553,8 +2862,6 @@
           <t>https://www.remotecall.com/kr/success-stories/maintenance/initech/</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr"/>
-      <c r="E125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -2570,8 +2877,6 @@
           <t>https://www.remotecall.com/kr/success-stories/mobile-device/lg-electronics-home/</t>
         </is>
       </c>
-      <c r="D126" t="inlineStr"/>
-      <c r="E126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -2587,8 +2892,11 @@
           <t>https://www.remotecall.com/kr/success-stories/mobile-device/ntt-docomo/</t>
         </is>
       </c>
-      <c r="D127" t="inlineStr"/>
-      <c r="E127" t="inlineStr"/>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -2604,8 +2912,11 @@
           <t>https://www.remotecall.com/kr/success-stories/remotecall-face/yuanta-securities/</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr"/>
-      <c r="E128" t="inlineStr"/>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -2621,8 +2932,6 @@
           <t>https://www.remotecall.com/kr/success-stories/standard-chartered-bank-korea/</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr"/>
-      <c r="E129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -2638,8 +2947,11 @@
           <t>https://www.remotecall.com/kr/support/</t>
         </is>
       </c>
-      <c r="D130" t="inlineStr"/>
-      <c r="E130" t="inlineStr"/>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -2655,8 +2967,11 @@
           <t>https://www.remotecall.com/kr/support/download/</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr"/>
-      <c r="E131" t="inlineStr"/>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -2672,8 +2987,11 @@
           <t>https://www.remotecall.com/kr/support/guide</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr"/>
-      <c r="E132" t="inlineStr"/>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -2689,8 +3007,11 @@
           <t>https://www.remotecall.com/kr/support/guide/</t>
         </is>
       </c>
-      <c r="D133" t="inlineStr"/>
-      <c r="E133" t="inlineStr"/>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -2706,8 +3027,6 @@
           <t>https://www.remotecall.com/kr/support/notices</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr"/>
-      <c r="E134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -2723,8 +3042,6 @@
           <t>https://www.remotecall.com/kr/support/notices/</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr"/>
-      <c r="E135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -2740,8 +3057,11 @@
           <t>https://www.remotecall.com/kr/support/notices/company</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr"/>
-      <c r="E136" t="inlineStr"/>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -2757,8 +3077,11 @@
           <t>https://www.remotecall.com/kr/support/notices/company/</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr"/>
-      <c r="E137" t="inlineStr"/>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -2774,8 +3097,6 @@
           <t>https://www.remotecall.com/kr/support/notices/company/feed/</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr"/>
-      <c r="E138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -2791,8 +3112,11 @@
           <t>https://www.remotecall.com/kr/support/notices/company/office-holiday-notice-202102/</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr"/>
-      <c r="E139" t="inlineStr"/>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -2808,8 +3132,6 @@
           <t>https://www.remotecall.com/kr/support/notices/company/office-holiday-notice-202109/</t>
         </is>
       </c>
-      <c r="D140" t="inlineStr"/>
-      <c r="E140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -2825,8 +3147,11 @@
           <t>https://www.remotecall.com/kr/support/notices/company/office-holiday-notice-202111/</t>
         </is>
       </c>
-      <c r="D141" t="inlineStr"/>
-      <c r="E141" t="inlineStr"/>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -2842,8 +3167,11 @@
           <t>https://www.remotecall.com/kr/support/notices/company/office-holiday-notice-20211117/</t>
         </is>
       </c>
-      <c r="D142" t="inlineStr"/>
-      <c r="E142" t="inlineStr"/>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -2859,8 +3187,11 @@
           <t>https://www.remotecall.com/kr/support/notices/company/office-holiday-notice-20211224/</t>
         </is>
       </c>
-      <c r="D143" t="inlineStr"/>
-      <c r="E143" t="inlineStr"/>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -2876,8 +3207,11 @@
           <t>https://www.remotecall.com/kr/support/notices/company/office-holiday-notice-202202/</t>
         </is>
       </c>
-      <c r="D144" t="inlineStr"/>
-      <c r="E144" t="inlineStr"/>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -2893,8 +3227,11 @@
           <t>https://www.remotecall.com/kr/support/notices/company/office-holiday-notice-202205/</t>
         </is>
       </c>
-      <c r="D145" t="inlineStr"/>
-      <c r="E145" t="inlineStr"/>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -2910,8 +3247,11 @@
           <t>https://www.remotecall.com/kr/support/notices/company/office-holiday-notice-20220506/</t>
         </is>
       </c>
-      <c r="D146" t="inlineStr"/>
-      <c r="E146" t="inlineStr"/>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -2927,8 +3267,11 @@
           <t>https://www.remotecall.com/kr/support/notices/company/office-holiday-notice-202212/</t>
         </is>
       </c>
-      <c r="D147" t="inlineStr"/>
-      <c r="E147" t="inlineStr"/>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -2944,8 +3287,11 @@
           <t>https://www.remotecall.com/kr/support/notices/company/office-holiday-notice-202405/</t>
         </is>
       </c>
-      <c r="D148" t="inlineStr"/>
-      <c r="E148" t="inlineStr"/>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -2961,8 +3307,11 @@
           <t>https://www.remotecall.com/kr/support/notices/company/page/2/</t>
         </is>
       </c>
-      <c r="D149" t="inlineStr"/>
-      <c r="E149" t="inlineStr"/>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -2978,8 +3327,11 @@
           <t>https://www.remotecall.com/kr/support/notices/company/page/3/</t>
         </is>
       </c>
-      <c r="D150" t="inlineStr"/>
-      <c r="E150" t="inlineStr"/>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -2995,8 +3347,11 @@
           <t>https://www.remotecall.com/kr/support/notices/event</t>
         </is>
       </c>
-      <c r="D151" t="inlineStr"/>
-      <c r="E151" t="inlineStr"/>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -3012,8 +3367,11 @@
           <t>https://www.remotecall.com/kr/support/notices/event/</t>
         </is>
       </c>
-      <c r="D152" t="inlineStr"/>
-      <c r="E152" t="inlineStr"/>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -3029,8 +3387,11 @@
           <t>https://www.remotecall.com/kr/support/notices/event/4th-fesrival-2020/</t>
         </is>
       </c>
-      <c r="D153" t="inlineStr"/>
-      <c r="E153" t="inlineStr"/>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -3046,8 +3407,11 @@
           <t>https://www.remotecall.com/kr/support/notices/event/event-public-solution-market-24th/</t>
         </is>
       </c>
-      <c r="D154" t="inlineStr"/>
-      <c r="E154" t="inlineStr"/>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -3063,8 +3427,11 @@
           <t>https://www.remotecall.com/kr/support/notices/event/japan-it-week-2018-spring-review/</t>
         </is>
       </c>
-      <c r="D155" t="inlineStr"/>
-      <c r="E155" t="inlineStr"/>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -3080,8 +3447,11 @@
           <t>https://www.remotecall.com/kr/support/notices/event/mwc-2018-barcelona-review/</t>
         </is>
       </c>
-      <c r="D156" t="inlineStr"/>
-      <c r="E156" t="inlineStr"/>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -3097,8 +3467,11 @@
           <t>https://www.remotecall.com/kr/support/notices/event/page/2/</t>
         </is>
       </c>
-      <c r="D157" t="inlineStr"/>
-      <c r="E157" t="inlineStr"/>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -3114,8 +3487,11 @@
           <t>https://www.remotecall.com/kr/support/notices/event/page/3/</t>
         </is>
       </c>
-      <c r="D158" t="inlineStr"/>
-      <c r="E158" t="inlineStr"/>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -3131,8 +3507,11 @@
           <t>https://www.remotecall.com/kr/support/notices/event/page/6/</t>
         </is>
       </c>
-      <c r="D159" t="inlineStr"/>
-      <c r="E159" t="inlineStr"/>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -3148,8 +3527,11 @@
           <t>https://www.remotecall.com/kr/support/notices/event/public-solution-2018-review/</t>
         </is>
       </c>
-      <c r="D160" t="inlineStr"/>
-      <c r="E160" t="inlineStr"/>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -3165,8 +3547,11 @@
           <t>https://www.remotecall.com/kr/support/notices/event/public-solution-2019-review/</t>
         </is>
       </c>
-      <c r="D161" t="inlineStr"/>
-      <c r="E161" t="inlineStr"/>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -3182,8 +3567,11 @@
           <t>https://www.remotecall.com/kr/support/notices/event/rsupport-tech-day-2018-review/</t>
         </is>
       </c>
-      <c r="D162" t="inlineStr"/>
-      <c r="E162" t="inlineStr"/>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -3199,8 +3587,11 @@
           <t>https://www.remotecall.com/kr/support/notices/event/rsupport-techday-2018-review/</t>
         </is>
       </c>
-      <c r="D163" t="inlineStr"/>
-      <c r="E163" t="inlineStr"/>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -3216,8 +3607,11 @@
           <t>https://www.remotecall.com/kr/support/notices/event/smart-tech-korea-2022/</t>
         </is>
       </c>
-      <c r="D164" t="inlineStr"/>
-      <c r="E164" t="inlineStr"/>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -3233,8 +3627,11 @@
           <t>https://www.remotecall.com/kr/support/notices/event/world-it-show-2018/</t>
         </is>
       </c>
-      <c r="D165" t="inlineStr"/>
-      <c r="E165" t="inlineStr"/>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -3250,8 +3647,11 @@
           <t>https://www.remotecall.com/kr/support/notices/page/2/</t>
         </is>
       </c>
-      <c r="D166" t="inlineStr"/>
-      <c r="E166" t="inlineStr"/>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -3267,8 +3667,11 @@
           <t>https://www.remotecall.com/kr/support/notices/page/26/</t>
         </is>
       </c>
-      <c r="D167" t="inlineStr"/>
-      <c r="E167" t="inlineStr"/>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -3284,8 +3687,11 @@
           <t>https://www.remotecall.com/kr/support/notices/page/27/</t>
         </is>
       </c>
-      <c r="D168" t="inlineStr"/>
-      <c r="E168" t="inlineStr"/>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -3301,8 +3707,11 @@
           <t>https://www.remotecall.com/kr/support/notices/page/28/</t>
         </is>
       </c>
-      <c r="D169" t="inlineStr"/>
-      <c r="E169" t="inlineStr"/>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -3318,8 +3727,11 @@
           <t>https://www.remotecall.com/kr/support/notices/page/3/</t>
         </is>
       </c>
-      <c r="D170" t="inlineStr"/>
-      <c r="E170" t="inlineStr"/>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -3335,8 +3747,11 @@
           <t>https://www.remotecall.com/kr/support/notices/page/4/</t>
         </is>
       </c>
-      <c r="D171" t="inlineStr"/>
-      <c r="E171" t="inlineStr"/>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -3352,8 +3767,11 @@
           <t>https://www.remotecall.com/kr/support/notices/page/5/</t>
         </is>
       </c>
-      <c r="D172" t="inlineStr"/>
-      <c r="E172" t="inlineStr"/>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -3369,8 +3787,11 @@
           <t>https://www.remotecall.com/kr/support/notices/press</t>
         </is>
       </c>
-      <c r="D173" t="inlineStr"/>
-      <c r="E173" t="inlineStr"/>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -3386,8 +3807,11 @@
           <t>https://www.remotecall.com/kr/support/notices/press/huawei-contract-remotecall-mobilepack/</t>
         </is>
       </c>
-      <c r="D174" t="inlineStr"/>
-      <c r="E174" t="inlineStr"/>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -3403,8 +3827,11 @@
           <t>https://www.remotecall.com/kr/support/notices/press/mobile-award-2019-winner/</t>
         </is>
       </c>
-      <c r="D175" t="inlineStr"/>
-      <c r="E175" t="inlineStr"/>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -3420,8 +3847,11 @@
           <t>https://www.remotecall.com/kr/support/notices/press/remotecall-get-gs1st-certfication/</t>
         </is>
       </c>
-      <c r="D176" t="inlineStr"/>
-      <c r="E176" t="inlineStr"/>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -3437,8 +3867,11 @@
           <t>https://www.remotecall.com/kr/support/notices/press/swaward-winner-2016/</t>
         </is>
       </c>
-      <c r="D177" t="inlineStr"/>
-      <c r="E177" t="inlineStr"/>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -3454,8 +3887,11 @@
           <t>https://www.remotecall.com/kr/support/notices/press/worldclass-product-korea-2017/</t>
         </is>
       </c>
-      <c r="D178" t="inlineStr"/>
-      <c r="E178" t="inlineStr"/>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -3471,8 +3907,11 @@
           <t>https://www.remotecall.com/kr/support/notices/promotion</t>
         </is>
       </c>
-      <c r="D179" t="inlineStr"/>
-      <c r="E179" t="inlineStr"/>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -3488,8 +3927,11 @@
           <t>https://www.remotecall.com/kr/support/notices/promotion/</t>
         </is>
       </c>
-      <c r="D180" t="inlineStr"/>
-      <c r="E180" t="inlineStr"/>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -3505,8 +3947,11 @@
           <t>https://www.remotecall.com/kr/support/notices/promotion/2023-non-face-voucher-apply/</t>
         </is>
       </c>
-      <c r="D181" t="inlineStr"/>
-      <c r="E181" t="inlineStr"/>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -3522,8 +3967,11 @@
           <t>https://www.remotecall.com/kr/support/notices/promotion/2023-rcvp-survey-event/</t>
         </is>
       </c>
-      <c r="D182" t="inlineStr"/>
-      <c r="E182" t="inlineStr"/>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -3539,8 +3987,11 @@
           <t>https://www.remotecall.com/kr/support/notices/promotion/2023-recommend-event/</t>
         </is>
       </c>
-      <c r="D183" t="inlineStr"/>
-      <c r="E183" t="inlineStr"/>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -3556,8 +4007,11 @@
           <t>https://www.remotecall.com/kr/support/notices/promotion/2024-cloud-voucher/</t>
         </is>
       </c>
-      <c r="D184" t="inlineStr"/>
-      <c r="E184" t="inlineStr"/>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -3573,8 +4027,11 @@
           <t>https://www.remotecall.com/kr/support/notices/promotion/free-remotecall-and-free-coffee/</t>
         </is>
       </c>
-      <c r="D185" t="inlineStr"/>
-      <c r="E185" t="inlineStr"/>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -3590,8 +4047,11 @@
           <t>https://www.remotecall.com/kr/support/notices/promotion/notice-event-winner-20221129/</t>
         </is>
       </c>
-      <c r="D186" t="inlineStr"/>
-      <c r="E186" t="inlineStr"/>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -3607,8 +4067,11 @@
           <t>https://www.remotecall.com/kr/support/notices/promotion/page/2/</t>
         </is>
       </c>
-      <c r="D187" t="inlineStr"/>
-      <c r="E187" t="inlineStr"/>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -3624,8 +4087,11 @@
           <t>https://www.remotecall.com/kr/support/notices/promotion/page/3/</t>
         </is>
       </c>
-      <c r="D188" t="inlineStr"/>
-      <c r="E188" t="inlineStr"/>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -3641,8 +4107,11 @@
           <t>https://www.remotecall.com/kr/support/notices/promotion/page/5/</t>
         </is>
       </c>
-      <c r="D189" t="inlineStr"/>
-      <c r="E189" t="inlineStr"/>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -3658,8 +4127,11 @@
           <t>https://www.remotecall.com/kr/support/notices/promotion/promotion-airchallenge/</t>
         </is>
       </c>
-      <c r="D190" t="inlineStr"/>
-      <c r="E190" t="inlineStr"/>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -3675,8 +4147,11 @@
           <t>https://www.remotecall.com/kr/support/notices/promotion/rsupport-year-end-dinner-2025/</t>
         </is>
       </c>
-      <c r="D191" t="inlineStr"/>
-      <c r="E191" t="inlineStr"/>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -3692,8 +4167,11 @@
           <t>https://www.remotecall.com/kr/support/notices/promotion/sales-promotion-2308/</t>
         </is>
       </c>
-      <c r="D192" t="inlineStr"/>
-      <c r="E192" t="inlineStr"/>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -3709,8 +4187,11 @@
           <t>https://www.remotecall.com/kr/support/notices/promotion/salespromotion2024/</t>
         </is>
       </c>
-      <c r="D193" t="inlineStr"/>
-      <c r="E193" t="inlineStr"/>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -3726,8 +4207,11 @@
           <t>https://www.remotecall.com/kr/support/notices/service</t>
         </is>
       </c>
-      <c r="D194" t="inlineStr"/>
-      <c r="E194" t="inlineStr"/>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -3743,8 +4227,11 @@
           <t>https://www.remotecall.com/kr/support/notices/service/</t>
         </is>
       </c>
-      <c r="D195" t="inlineStr"/>
-      <c r="E195" t="inlineStr"/>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -3760,8 +4247,6 @@
           <t>https://www.remotecall.com/kr/support/notices/service/feed/</t>
         </is>
       </c>
-      <c r="D196" t="inlineStr"/>
-      <c r="E196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -3777,8 +4262,11 @@
           <t>https://www.remotecall.com/kr/support/notices/service/page/13/</t>
         </is>
       </c>
-      <c r="D197" t="inlineStr"/>
-      <c r="E197" t="inlineStr"/>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -3794,8 +4282,11 @@
           <t>https://www.remotecall.com/kr/support/notices/service/page/2/</t>
         </is>
       </c>
-      <c r="D198" t="inlineStr"/>
-      <c r="E198" t="inlineStr"/>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -3811,8 +4302,11 @@
           <t>https://www.remotecall.com/kr/support/notices/service/page/3/</t>
         </is>
       </c>
-      <c r="D199" t="inlineStr"/>
-      <c r="E199" t="inlineStr"/>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -3828,8 +4322,11 @@
           <t>https://www.remotecall.com/kr/support/notices/service/product-update-notice-20231116/</t>
         </is>
       </c>
-      <c r="D200" t="inlineStr"/>
-      <c r="E200" t="inlineStr"/>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -3845,8 +4342,11 @@
           <t>https://www.remotecall.com/kr/support/notices/service/product-update-notice-20231219/</t>
         </is>
       </c>
-      <c r="D201" t="inlineStr"/>
-      <c r="E201" t="inlineStr"/>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -3862,8 +4362,11 @@
           <t>https://www.remotecall.com/kr/support/notices/service/product-update-notice-20240130/</t>
         </is>
       </c>
-      <c r="D202" t="inlineStr"/>
-      <c r="E202" t="inlineStr"/>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -3879,8 +4382,11 @@
           <t>https://www.remotecall.com/kr/support/notices/service/product-update-notice-20240625/</t>
         </is>
       </c>
-      <c r="D203" t="inlineStr"/>
-      <c r="E203" t="inlineStr"/>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -3896,8 +4402,11 @@
           <t>https://www.remotecall.com/kr/support/notices/service/product-update-notice-20240821/</t>
         </is>
       </c>
-      <c r="D204" t="inlineStr"/>
-      <c r="E204" t="inlineStr"/>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -3913,8 +4422,11 @@
           <t>https://www.remotecall.com/kr/support/notices/service/product-update-notice-20240924/</t>
         </is>
       </c>
-      <c r="D205" t="inlineStr"/>
-      <c r="E205" t="inlineStr"/>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -3930,8 +4442,11 @@
           <t>https://www.remotecall.com/kr/support/notices/service/product-update-notice-20241126/</t>
         </is>
       </c>
-      <c r="D206" t="inlineStr"/>
-      <c r="E206" t="inlineStr"/>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -3947,8 +4462,11 @@
           <t>https://www.remotecall.com/kr/support/notices/service/product-update-notice-20250527/</t>
         </is>
       </c>
-      <c r="D207" t="inlineStr"/>
-      <c r="E207" t="inlineStr"/>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -3964,8 +4482,11 @@
           <t>https://www.remotecall.com/kr/support/notices/service/product-update-notice-20250819/</t>
         </is>
       </c>
-      <c r="D208" t="inlineStr"/>
-      <c r="E208" t="inlineStr"/>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -3981,8 +4502,11 @@
           <t>https://www.remotecall.com/kr/support/notices/service/product-update-notice-20251125/</t>
         </is>
       </c>
-      <c r="D209" t="inlineStr"/>
-      <c r="E209" t="inlineStr"/>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -3998,8 +4522,11 @@
           <t>https://www.remotecall.com/kr/support/notices/service/product-update-notice-20260224/</t>
         </is>
       </c>
-      <c r="D210" t="inlineStr"/>
-      <c r="E210" t="inlineStr"/>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -4015,8 +4542,11 @@
           <t>https://www.remotecall.com/kr/support/notices/service/product-update-notice-20260403/</t>
         </is>
       </c>
-      <c r="D211" t="inlineStr"/>
-      <c r="E211" t="inlineStr"/>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -4032,8 +4562,11 @@
           <t>https://www.remotecall.com/kr/support/notices/service/product-update-notice-20260421/</t>
         </is>
       </c>
-      <c r="D212" t="inlineStr"/>
-      <c r="E212" t="inlineStr"/>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -4049,8 +4582,11 @@
           <t>https://www.remotecall.com/kr/support/notices/service/product-update-notice-20260507/</t>
         </is>
       </c>
-      <c r="D213" t="inlineStr"/>
-      <c r="E213" t="inlineStr"/>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -4066,8 +4602,11 @@
           <t>https://www.remotecall.com/kr/support/notices/service/product-update-notice-20260527/</t>
         </is>
       </c>
-      <c r="D214" t="inlineStr"/>
-      <c r="E214" t="inlineStr"/>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -4083,8 +4622,11 @@
           <t>https://www.remotecall.com/kr/support/notices/service/product-update-notice-20260629/</t>
         </is>
       </c>
-      <c r="D215" t="inlineStr"/>
-      <c r="E215" t="inlineStr"/>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -4100,8 +4642,11 @@
           <t>https://www.remotecall.com/kr/support/notices/service/restoration-complete-20250513/</t>
         </is>
       </c>
-      <c r="D216" t="inlineStr"/>
-      <c r="E216" t="inlineStr"/>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -4117,8 +4662,11 @@
           <t>https://www.remotecall.com/kr/support/notices/service/safe-automatic-renewal-contract-23020201/</t>
         </is>
       </c>
-      <c r="D217" t="inlineStr"/>
-      <c r="E217" t="inlineStr"/>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -4134,8 +4682,11 @@
           <t>https://www.remotecall.com/kr/support/notices/service/server-info-exchange-notice-20240201/</t>
         </is>
       </c>
-      <c r="D218" t="inlineStr"/>
-      <c r="E218" t="inlineStr"/>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -4151,8 +4702,11 @@
           <t>https://www.remotecall.com/kr/support/notices/service/server-replacement-notice-20150420/</t>
         </is>
       </c>
-      <c r="D219" t="inlineStr"/>
-      <c r="E219" t="inlineStr"/>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -4168,8 +4722,11 @@
           <t>https://www.remotecall.com/kr/support/notices/service/service-specification-notice-20231011/</t>
         </is>
       </c>
-      <c r="D220" t="inlineStr"/>
-      <c r="E220" t="inlineStr"/>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -4185,8 +4742,11 @@
           <t>https://www.remotecall.com/kr/support/notices/service/system-maintenance-notice-20150119/</t>
         </is>
       </c>
-      <c r="D221" t="inlineStr"/>
-      <c r="E221" t="inlineStr"/>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -4202,8 +4762,11 @@
           <t>https://www.remotecall.com/kr/support/notices/service/system-maintenance-notice-20150323/</t>
         </is>
       </c>
-      <c r="D222" t="inlineStr"/>
-      <c r="E222" t="inlineStr"/>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -4219,8 +4782,11 @@
           <t>https://www.remotecall.com/kr/support/notices/service/system-maintenance-notice-20150420/</t>
         </is>
       </c>
-      <c r="D223" t="inlineStr"/>
-      <c r="E223" t="inlineStr"/>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -4236,8 +4802,11 @@
           <t>https://www.remotecall.com/kr/support/notices/service/system-maintenance-notice-20260417/</t>
         </is>
       </c>
-      <c r="D224" t="inlineStr"/>
-      <c r="E224" t="inlineStr"/>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -4253,8 +4822,11 @@
           <t>https://www.remotecall.com/kr/support/notices/service/update-notice-20141111/</t>
         </is>
       </c>
-      <c r="D225" t="inlineStr"/>
-      <c r="E225" t="inlineStr"/>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -4270,8 +4842,11 @@
           <t>https://www.remotecall.com/kr/support/notices/service/update-notice-20141201/</t>
         </is>
       </c>
-      <c r="D226" t="inlineStr"/>
-      <c r="E226" t="inlineStr"/>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -4287,8 +4862,11 @@
           <t>https://www.remotecall.com/kr/support/notices/service/update-notice-20150202/</t>
         </is>
       </c>
-      <c r="D227" t="inlineStr"/>
-      <c r="E227" t="inlineStr"/>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -4304,8 +4882,11 @@
           <t>https://www.remotecall.com/kr/support/notices/service/windows-defender-delay-20250205/</t>
         </is>
       </c>
-      <c r="D228" t="inlineStr"/>
-      <c r="E228" t="inlineStr"/>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -4321,8 +4902,11 @@
           <t>https://www.remotecall.com/kr/support/notices/website</t>
         </is>
       </c>
-      <c r="D229" t="inlineStr"/>
-      <c r="E229" t="inlineStr"/>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -4338,8 +4922,11 @@
           <t>https://www.remotecall.com/kr/support/notices/website/</t>
         </is>
       </c>
-      <c r="D230" t="inlineStr"/>
-      <c r="E230" t="inlineStr"/>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -4355,8 +4942,11 @@
           <t>https://www.remotecall.com/kr/support/notices/website/location-notice-20220929/</t>
         </is>
       </c>
-      <c r="D231" t="inlineStr"/>
-      <c r="E231" t="inlineStr"/>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -4372,8 +4962,11 @@
           <t>https://www.remotecall.com/kr/support/notices/website/page/2/</t>
         </is>
       </c>
-      <c r="D232" t="inlineStr"/>
-      <c r="E232" t="inlineStr"/>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -4389,8 +4982,11 @@
           <t>https://www.remotecall.com/kr/support/notices/website/privacy-notice-20170906/</t>
         </is>
       </c>
-      <c r="D233" t="inlineStr"/>
-      <c r="E233" t="inlineStr"/>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -4406,8 +5002,11 @@
           <t>https://www.remotecall.com/kr/support/notices/website/privacy-notice-20171030/</t>
         </is>
       </c>
-      <c r="D234" t="inlineStr"/>
-      <c r="E234" t="inlineStr"/>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -4423,8 +5022,11 @@
           <t>https://www.remotecall.com/kr/support/notices/website/privacy-notice-20180105/</t>
         </is>
       </c>
-      <c r="D235" t="inlineStr"/>
-      <c r="E235" t="inlineStr"/>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -4440,8 +5042,11 @@
           <t>https://www.remotecall.com/kr/support/notices/website/privacy-notice-20180130/</t>
         </is>
       </c>
-      <c r="D236" t="inlineStr"/>
-      <c r="E236" t="inlineStr"/>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -4457,8 +5062,11 @@
           <t>https://www.remotecall.com/kr/support/notices/website/privacy-notice-20180501/</t>
         </is>
       </c>
-      <c r="D237" t="inlineStr"/>
-      <c r="E237" t="inlineStr"/>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -4474,8 +5082,11 @@
           <t>https://www.remotecall.com/kr/support/notices/website/privacy-notice-20200602/</t>
         </is>
       </c>
-      <c r="D238" t="inlineStr"/>
-      <c r="E238" t="inlineStr"/>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -4491,8 +5102,11 @@
           <t>https://www.remotecall.com/kr/support/notices/website/privacy-notice-20210806/</t>
         </is>
       </c>
-      <c r="D239" t="inlineStr"/>
-      <c r="E239" t="inlineStr"/>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -4508,8 +5122,11 @@
           <t>https://www.remotecall.com/kr/support/notices/website/privacy-policy-notice-20231223/</t>
         </is>
       </c>
-      <c r="D240" t="inlineStr"/>
-      <c r="E240" t="inlineStr"/>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -4525,8 +5142,11 @@
           <t>https://www.remotecall.com/kr/support/notices/website/terms-notice-20210216/</t>
         </is>
       </c>
-      <c r="D241" t="inlineStr"/>
-      <c r="E241" t="inlineStr"/>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -4542,8 +5162,11 @@
           <t>https://www.remotecall.com/kr/support/notices_renew/promotion/free-remotecall-and-free-coffee/</t>
         </is>
       </c>
-      <c r="D242" t="inlineStr"/>
-      <c r="E242" t="inlineStr"/>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -4559,8 +5182,11 @@
           <t>https://www.remotecall.com/kr/support/resources/</t>
         </is>
       </c>
-      <c r="D243" t="inlineStr"/>
-      <c r="E243" t="inlineStr"/>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -4576,8 +5202,11 @@
           <t>https://www.remotecall.com/kr/support/tutorials/</t>
         </is>
       </c>
-      <c r="D244" t="inlineStr"/>
-      <c r="E244" t="inlineStr"/>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -4593,8 +5222,11 @@
           <t>https://www.remotecall.com/kr/support/tutorials/how-to-use-remotecall-web/</t>
         </is>
       </c>
-      <c r="D245" t="inlineStr"/>
-      <c r="E245" t="inlineStr"/>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -4610,8 +5242,11 @@
           <t>https://www.remotecall.com/kr/support/update-history/update-20210322/</t>
         </is>
       </c>
-      <c r="D246" t="inlineStr"/>
-      <c r="E246" t="inlineStr"/>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -4627,8 +5262,11 @@
           <t>https://www.remotecall.com/kr/support/update-history/update-20210524/</t>
         </is>
       </c>
-      <c r="D247" t="inlineStr"/>
-      <c r="E247" t="inlineStr"/>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -4644,8 +5282,11 @@
           <t>https://www.remotecall.com/kr/support/update-history/update-20210705/</t>
         </is>
       </c>
-      <c r="D248" t="inlineStr"/>
-      <c r="E248" t="inlineStr"/>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -4661,8 +5302,11 @@
           <t>https://www.remotecall.com/kr/support/update-history/update-20211020/</t>
         </is>
       </c>
-      <c r="D249" t="inlineStr"/>
-      <c r="E249" t="inlineStr"/>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -4678,8 +5322,11 @@
           <t>https://www.remotecall.com/kr/support/update-history/update-20220111/</t>
         </is>
       </c>
-      <c r="D250" t="inlineStr"/>
-      <c r="E250" t="inlineStr"/>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -4695,8 +5342,11 @@
           <t>https://www.remotecall.com/kr/support/update-history/update-20220414/</t>
         </is>
       </c>
-      <c r="D251" t="inlineStr"/>
-      <c r="E251" t="inlineStr"/>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -4712,8 +5362,11 @@
           <t>https://www.remotecall.com/kr/support/update-history/update-20221115/</t>
         </is>
       </c>
-      <c r="D252" t="inlineStr"/>
-      <c r="E252" t="inlineStr"/>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -4729,8 +5382,11 @@
           <t>https://www.remotecall.com/kr/support/update-history/update-20230411/</t>
         </is>
       </c>
-      <c r="D253" t="inlineStr"/>
-      <c r="E253" t="inlineStr"/>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -4746,8 +5402,11 @@
           <t>https://www.remotecall.com/kr/support/update-history/update-20231116/</t>
         </is>
       </c>
-      <c r="D254" t="inlineStr"/>
-      <c r="E254" t="inlineStr"/>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -4763,8 +5422,11 @@
           <t>https://www.remotecall.com/kr/support/update-history/update-20240625/</t>
         </is>
       </c>
-      <c r="D255" t="inlineStr"/>
-      <c r="E255" t="inlineStr"/>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -4780,8 +5442,11 @@
           <t>https://www.remotecall.com/kr/support/update-history_renew/</t>
         </is>
       </c>
-      <c r="D256" t="inlineStr"/>
-      <c r="E256" t="inlineStr"/>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -4797,8 +5462,11 @@
           <t>https://www.remotecall.com/kr/support/videos</t>
         </is>
       </c>
-      <c r="D257" t="inlineStr"/>
-      <c r="E257" t="inlineStr"/>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -4814,8 +5482,11 @@
           <t>https://www.remotecall.com/kr/support/videos/</t>
         </is>
       </c>
-      <c r="D258" t="inlineStr"/>
-      <c r="E258" t="inlineStr"/>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -4831,8 +5502,11 @@
           <t>https://www.remotecall.com/kr/terms-of-service/</t>
         </is>
       </c>
-      <c r="D259" t="inlineStr"/>
-      <c r="E259" t="inlineStr"/>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -4848,8 +5522,11 @@
           <t>https://www.remotecall.com/kr/update-history/update-20231116/</t>
         </is>
       </c>
-      <c r="D260" t="inlineStr"/>
-      <c r="E260" t="inlineStr"/>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -4865,8 +5542,6 @@
           <t>https://www.remotecall.com/kr/use-cases/</t>
         </is>
       </c>
-      <c r="D261" t="inlineStr"/>
-      <c r="E261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -4882,8 +5557,11 @@
           <t>https://www.remotecall.com/kr/use-cases/library/</t>
         </is>
       </c>
-      <c r="D262" t="inlineStr"/>
-      <c r="E262" t="inlineStr"/>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -4899,8 +5577,6 @@
           <t>https://www.remotecall.com/kr/use-cases/success-stories/</t>
         </is>
       </c>
-      <c r="D263" t="inlineStr"/>
-      <c r="E263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -4916,8 +5592,11 @@
           <t>https://www.remotecall.com/kr/use-cases/success-stories/etc/</t>
         </is>
       </c>
-      <c r="D264" t="inlineStr"/>
-      <c r="E264" t="inlineStr"/>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -4933,8 +5612,11 @@
           <t>https://www.remotecall.com/kr/use-cases/success-stories/etc/bundang-jesaeng-hospital</t>
         </is>
       </c>
-      <c r="D265" t="inlineStr"/>
-      <c r="E265" t="inlineStr"/>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -4950,8 +5632,11 @@
           <t>https://www.remotecall.com/kr/use-cases/success-stories/etc/bundang-jesaeng-hospital/</t>
         </is>
       </c>
-      <c r="D266" t="inlineStr"/>
-      <c r="E266" t="inlineStr"/>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -4967,8 +5652,11 @@
           <t>https://www.remotecall.com/kr/use-cases/success-stories/etc/kakaoent</t>
         </is>
       </c>
-      <c r="D267" t="inlineStr"/>
-      <c r="E267" t="inlineStr"/>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -4984,8 +5672,11 @@
           <t>https://www.remotecall.com/kr/use-cases/success-stories/etc/kakaoent/</t>
         </is>
       </c>
-      <c r="D268" t="inlineStr"/>
-      <c r="E268" t="inlineStr"/>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -5001,8 +5692,11 @@
           <t>https://www.remotecall.com/kr/use-cases/success-stories/etc/osstem-implant</t>
         </is>
       </c>
-      <c r="D269" t="inlineStr"/>
-      <c r="E269" t="inlineStr"/>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -5018,8 +5712,11 @@
           <t>https://www.remotecall.com/kr/use-cases/success-stories/etc/osstem-implant/</t>
         </is>
       </c>
-      <c r="D270" t="inlineStr"/>
-      <c r="E270" t="inlineStr"/>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -5035,8 +5732,11 @@
           <t>https://www.remotecall.com/kr/use-cases/success-stories/financ/kbank/</t>
         </is>
       </c>
-      <c r="D271" t="inlineStr"/>
-      <c r="E271" t="inlineStr"/>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -5052,8 +5752,11 @@
           <t>https://www.remotecall.com/kr/use-cases/success-stories/finance/</t>
         </is>
       </c>
-      <c r="D272" t="inlineStr"/>
-      <c r="E272" t="inlineStr"/>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -5069,8 +5772,11 @@
           <t>https://www.remotecall.com/kr/use-cases/success-stories/finance/bbcn-bank</t>
         </is>
       </c>
-      <c r="D273" t="inlineStr"/>
-      <c r="E273" t="inlineStr"/>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -5086,8 +5792,11 @@
           <t>https://www.remotecall.com/kr/use-cases/success-stories/finance/bbcn-bank/</t>
         </is>
       </c>
-      <c r="D274" t="inlineStr"/>
-      <c r="E274" t="inlineStr"/>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -5103,8 +5812,11 @@
           <t>https://www.remotecall.com/kr/use-cases/success-stories/finance/busanbank</t>
         </is>
       </c>
-      <c r="D275" t="inlineStr"/>
-      <c r="E275" t="inlineStr"/>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -5120,8 +5832,11 @@
           <t>https://www.remotecall.com/kr/use-cases/success-stories/finance/busanbank/</t>
         </is>
       </c>
-      <c r="D276" t="inlineStr"/>
-      <c r="E276" t="inlineStr"/>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -5137,8 +5852,11 @@
           <t>https://www.remotecall.com/kr/use-cases/success-stories/finance/jbbank</t>
         </is>
       </c>
-      <c r="D277" t="inlineStr"/>
-      <c r="E277" t="inlineStr"/>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -5154,8 +5872,11 @@
           <t>https://www.remotecall.com/kr/use-cases/success-stories/finance/jbbank/</t>
         </is>
       </c>
-      <c r="D278" t="inlineStr"/>
-      <c r="E278" t="inlineStr"/>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -5171,8 +5892,11 @@
           <t>https://www.remotecall.com/kr/use-cases/success-stories/finance/k-internetbank</t>
         </is>
       </c>
-      <c r="D279" t="inlineStr"/>
-      <c r="E279" t="inlineStr"/>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -5188,8 +5912,11 @@
           <t>https://www.remotecall.com/kr/use-cases/success-stories/finance/k-internetbank/</t>
         </is>
       </c>
-      <c r="D280" t="inlineStr"/>
-      <c r="E280" t="inlineStr"/>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -5205,8 +5932,11 @@
           <t>https://www.remotecall.com/kr/use-cases/success-stories/finance/kbank</t>
         </is>
       </c>
-      <c r="D281" t="inlineStr"/>
-      <c r="E281" t="inlineStr"/>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -5222,8 +5952,11 @@
           <t>https://www.remotecall.com/kr/use-cases/success-stories/finance/kbank/</t>
         </is>
       </c>
-      <c r="D282" t="inlineStr"/>
-      <c r="E282" t="inlineStr"/>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -5239,8 +5972,11 @@
           <t>https://www.remotecall.com/kr/use-cases/success-stories/finance/kjbank</t>
         </is>
       </c>
-      <c r="D283" t="inlineStr"/>
-      <c r="E283" t="inlineStr"/>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -5256,8 +5992,11 @@
           <t>https://www.remotecall.com/kr/use-cases/success-stories/finance/kjbank/</t>
         </is>
       </c>
-      <c r="D284" t="inlineStr"/>
-      <c r="E284" t="inlineStr"/>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -5273,8 +6012,11 @@
           <t>https://www.remotecall.com/kr/use-cases/success-stories/finance/standard-chartered-bank-korea</t>
         </is>
       </c>
-      <c r="D285" t="inlineStr"/>
-      <c r="E285" t="inlineStr"/>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -5290,8 +6032,11 @@
           <t>https://www.remotecall.com/kr/use-cases/success-stories/finance/standard-chartered-bank-korea/</t>
         </is>
       </c>
-      <c r="D286" t="inlineStr"/>
-      <c r="E286" t="inlineStr"/>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -5307,8 +6052,11 @@
           <t>https://www.remotecall.com/kr/use-cases/success-stories/finance/woori-bank</t>
         </is>
       </c>
-      <c r="D287" t="inlineStr"/>
-      <c r="E287" t="inlineStr"/>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -5324,8 +6072,11 @@
           <t>https://www.remotecall.com/kr/use-cases/success-stories/finance/woori-bank/</t>
         </is>
       </c>
-      <c r="D288" t="inlineStr"/>
-      <c r="E288" t="inlineStr"/>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -5341,8 +6092,6 @@
           <t>https://www.remotecall.com/kr/use-cases/success-stories/finance/yuanta-securities</t>
         </is>
       </c>
-      <c r="D289" t="inlineStr"/>
-      <c r="E289" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -5358,8 +6107,6 @@
           <t>https://www.remotecall.com/kr/use-cases/success-stories/finance/yuanta-securities/</t>
         </is>
       </c>
-      <c r="D290" t="inlineStr"/>
-      <c r="E290" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -5375,8 +6122,11 @@
           <t>https://www.remotecall.com/kr/use-cases/success-stories/manufacturing/</t>
         </is>
       </c>
-      <c r="D291" t="inlineStr"/>
-      <c r="E291" t="inlineStr"/>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -5392,8 +6142,11 @@
           <t>https://www.remotecall.com/kr/use-cases/success-stories/manufacturing/ceragem</t>
         </is>
       </c>
-      <c r="D292" t="inlineStr"/>
-      <c r="E292" t="inlineStr"/>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -5409,8 +6162,11 @@
           <t>https://www.remotecall.com/kr/use-cases/success-stories/manufacturing/h-usedcar</t>
         </is>
       </c>
-      <c r="D293" t="inlineStr"/>
-      <c r="E293" t="inlineStr"/>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -5426,8 +6182,11 @@
           <t>https://www.remotecall.com/kr/use-cases/success-stories/manufacturing/h-usedcar/</t>
         </is>
       </c>
-      <c r="D294" t="inlineStr"/>
-      <c r="E294" t="inlineStr"/>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -5443,8 +6202,11 @@
           <t>https://www.remotecall.com/kr/use-cases/success-stories/manufacturing/huawei</t>
         </is>
       </c>
-      <c r="D295" t="inlineStr"/>
-      <c r="E295" t="inlineStr"/>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -5460,8 +6222,11 @@
           <t>https://www.remotecall.com/kr/use-cases/success-stories/manufacturing/kdnavien</t>
         </is>
       </c>
-      <c r="D296" t="inlineStr"/>
-      <c r="E296" t="inlineStr"/>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -5477,8 +6242,11 @@
           <t>https://www.remotecall.com/kr/use-cases/success-stories/manufacturing/kdnavien/</t>
         </is>
       </c>
-      <c r="D297" t="inlineStr"/>
-      <c r="E297" t="inlineStr"/>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -5494,8 +6262,11 @@
           <t>https://www.remotecall.com/kr/use-cases/success-stories/manufacturing/kia-car-repair</t>
         </is>
       </c>
-      <c r="D298" t="inlineStr"/>
-      <c r="E298" t="inlineStr"/>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -5511,8 +6282,11 @@
           <t>https://www.remotecall.com/kr/use-cases/success-stories/manufacturing/kia-car-repair/</t>
         </is>
       </c>
-      <c r="D299" t="inlineStr"/>
-      <c r="E299" t="inlineStr"/>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -5528,8 +6302,11 @@
           <t>https://www.remotecall.com/kr/use-cases/success-stories/manufacturing/lg-electronics-home</t>
         </is>
       </c>
-      <c r="D300" t="inlineStr"/>
-      <c r="E300" t="inlineStr"/>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -5545,8 +6322,11 @@
           <t>https://www.remotecall.com/kr/use-cases/success-stories/manufacturing/lg-electronics-home/</t>
         </is>
       </c>
-      <c r="D301" t="inlineStr"/>
-      <c r="E301" t="inlineStr"/>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -5562,8 +6342,11 @@
           <t>https://www.remotecall.com/kr/use-cases/success-stories/manufacturing/lg-electronics-mobile</t>
         </is>
       </c>
-      <c r="D302" t="inlineStr"/>
-      <c r="E302" t="inlineStr"/>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -5579,8 +6362,11 @@
           <t>https://www.remotecall.com/kr/use-cases/success-stories/manufacturing/lg-electronics-mobile/</t>
         </is>
       </c>
-      <c r="D303" t="inlineStr"/>
-      <c r="E303" t="inlineStr"/>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -5596,8 +6382,11 @@
           <t>https://www.remotecall.com/kr/use-cases/success-stories/manufacturing/mcloudsoft</t>
         </is>
       </c>
-      <c r="D304" t="inlineStr"/>
-      <c r="E304" t="inlineStr"/>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -5613,8 +6402,11 @@
           <t>https://www.remotecall.com/kr/use-cases/success-stories/manufacturing/mcloudsoft/</t>
         </is>
       </c>
-      <c r="D305" t="inlineStr"/>
-      <c r="E305" t="inlineStr"/>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -5630,8 +6422,11 @@
           <t>https://www.remotecall.com/kr/use-cases/success-stories/manufacturing/oneplus</t>
         </is>
       </c>
-      <c r="D306" t="inlineStr"/>
-      <c r="E306" t="inlineStr"/>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -5647,8 +6442,11 @@
           <t>https://www.remotecall.com/kr/use-cases/success-stories/manufacturing/oneplus/</t>
         </is>
       </c>
-      <c r="D307" t="inlineStr"/>
-      <c r="E307" t="inlineStr"/>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -5664,8 +6462,6 @@
           <t>https://www.remotecall.com/kr/use-cases/success-stories/manufacturing/page/2/</t>
         </is>
       </c>
-      <c r="D308" t="inlineStr"/>
-      <c r="E308" t="inlineStr"/>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -5681,8 +6477,11 @@
           <t>https://www.remotecall.com/kr/use-cases/success-stories/manufacturing/posco</t>
         </is>
       </c>
-      <c r="D309" t="inlineStr"/>
-      <c r="E309" t="inlineStr"/>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -5698,8 +6497,11 @@
           <t>https://www.remotecall.com/kr/use-cases/success-stories/manufacturing/puritech</t>
         </is>
       </c>
-      <c r="D310" t="inlineStr"/>
-      <c r="E310" t="inlineStr"/>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -5715,8 +6517,11 @@
           <t>https://www.remotecall.com/kr/use-cases/success-stories/manufacturing/puritech/</t>
         </is>
       </c>
-      <c r="D311" t="inlineStr"/>
-      <c r="E311" t="inlineStr"/>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -5732,8 +6537,11 @@
           <t>https://www.remotecall.com/kr/use-cases/success-stories/page/2/</t>
         </is>
       </c>
-      <c r="D312" t="inlineStr"/>
-      <c r="E312" t="inlineStr"/>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -5749,8 +6557,11 @@
           <t>https://www.remotecall.com/kr/use-cases/success-stories/page/3/</t>
         </is>
       </c>
-      <c r="D313" t="inlineStr"/>
-      <c r="E313" t="inlineStr"/>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -5766,8 +6577,11 @@
           <t>https://www.remotecall.com/kr/use-cases/success-stories/page/4/</t>
         </is>
       </c>
-      <c r="D314" t="inlineStr"/>
-      <c r="E314" t="inlineStr"/>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -5783,8 +6597,11 @@
           <t>https://www.remotecall.com/kr/use-cases/success-stories/page/5/</t>
         </is>
       </c>
-      <c r="D315" t="inlineStr"/>
-      <c r="E315" t="inlineStr"/>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -5800,8 +6617,11 @@
           <t>https://www.remotecall.com/kr/use-cases/success-stories/page/6/</t>
         </is>
       </c>
-      <c r="D316" t="inlineStr"/>
-      <c r="E316" t="inlineStr"/>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -5817,8 +6637,11 @@
           <t>https://www.remotecall.com/kr/use-cases/success-stories/public/</t>
         </is>
       </c>
-      <c r="D317" t="inlineStr"/>
-      <c r="E317" t="inlineStr"/>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -5834,8 +6657,11 @@
           <t>https://www.remotecall.com/kr/use-cases/success-stories/public/hanyang-university</t>
         </is>
       </c>
-      <c r="D318" t="inlineStr"/>
-      <c r="E318" t="inlineStr"/>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -5851,8 +6677,11 @@
           <t>https://www.remotecall.com/kr/use-cases/success-stories/public/hanyang-university/</t>
         </is>
       </c>
-      <c r="D319" t="inlineStr"/>
-      <c r="E319" t="inlineStr"/>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -5868,8 +6697,11 @@
           <t>https://www.remotecall.com/kr/use-cases/success-stories/public/kcgp</t>
         </is>
       </c>
-      <c r="D320" t="inlineStr"/>
-      <c r="E320" t="inlineStr"/>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -5885,8 +6717,11 @@
           <t>https://www.remotecall.com/kr/use-cases/success-stories/public/kcgp/</t>
         </is>
       </c>
-      <c r="D321" t="inlineStr"/>
-      <c r="E321" t="inlineStr"/>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -5902,8 +6737,11 @@
           <t>https://www.remotecall.com/kr/use-cases/success-stories/public/komipo</t>
         </is>
       </c>
-      <c r="D322" t="inlineStr"/>
-      <c r="E322" t="inlineStr"/>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -5919,8 +6757,11 @@
           <t>https://www.remotecall.com/kr/use-cases/success-stories/public/komipo/</t>
         </is>
       </c>
-      <c r="D323" t="inlineStr"/>
-      <c r="E323" t="inlineStr"/>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -5936,8 +6777,11 @@
           <t>https://www.remotecall.com/kr/use-cases/success-stories/public/sac</t>
         </is>
       </c>
-      <c r="D324" t="inlineStr"/>
-      <c r="E324" t="inlineStr"/>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -5953,8 +6797,11 @@
           <t>https://www.remotecall.com/kr/use-cases/success-stories/public/sac/</t>
         </is>
       </c>
-      <c r="D325" t="inlineStr"/>
-      <c r="E325" t="inlineStr"/>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -5970,8 +6817,11 @@
           <t>https://www.remotecall.com/kr/use-cases/success-stories/public/shanghai-normal-university</t>
         </is>
       </c>
-      <c r="D326" t="inlineStr"/>
-      <c r="E326" t="inlineStr"/>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -5987,8 +6837,11 @@
           <t>https://www.remotecall.com/kr/use-cases/success-stories/public/shanghai-normal-university/</t>
         </is>
       </c>
-      <c r="D327" t="inlineStr"/>
-      <c r="E327" t="inlineStr"/>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -6004,8 +6857,11 @@
           <t>https://www.remotecall.com/kr/use-cases/success-stories/public/woongjin-thinkbig</t>
         </is>
       </c>
-      <c r="D328" t="inlineStr"/>
-      <c r="E328" t="inlineStr"/>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -6021,8 +6877,11 @@
           <t>https://www.remotecall.com/kr/use-cases/success-stories/public/woongjin-thinkbig/</t>
         </is>
       </c>
-      <c r="D329" t="inlineStr"/>
-      <c r="E329" t="inlineStr"/>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -6038,8 +6897,6 @@
           <t>https://www.remotecall.com/kr/use-cases/success-stories/technology/</t>
         </is>
       </c>
-      <c r="D330" t="inlineStr"/>
-      <c r="E330" t="inlineStr"/>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -6055,8 +6912,11 @@
           <t>https://www.remotecall.com/kr/use-cases/success-stories/technology/aqualeaf</t>
         </is>
       </c>
-      <c r="D331" t="inlineStr"/>
-      <c r="E331" t="inlineStr"/>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -6072,8 +6932,11 @@
           <t>https://www.remotecall.com/kr/use-cases/success-stories/technology/cdnetworks</t>
         </is>
       </c>
-      <c r="D332" t="inlineStr"/>
-      <c r="E332" t="inlineStr"/>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -6089,8 +6952,11 @@
           <t>https://www.remotecall.com/kr/use-cases/success-stories/technology/cloocus</t>
         </is>
       </c>
-      <c r="D333" t="inlineStr"/>
-      <c r="E333" t="inlineStr"/>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -6106,8 +6972,11 @@
           <t>https://www.remotecall.com/kr/use-cases/success-stories/technology/coworks-it</t>
         </is>
       </c>
-      <c r="D334" t="inlineStr"/>
-      <c r="E334" t="inlineStr"/>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -6123,8 +6992,11 @@
           <t>https://www.remotecall.com/kr/use-cases/success-stories/technology/coworks-it/</t>
         </is>
       </c>
-      <c r="D335" t="inlineStr"/>
-      <c r="E335" t="inlineStr"/>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -6140,8 +7012,11 @@
           <t>https://www.remotecall.com/kr/use-cases/success-stories/technology/cresoty</t>
         </is>
       </c>
-      <c r="D336" t="inlineStr"/>
-      <c r="E336" t="inlineStr"/>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -6157,8 +7032,11 @@
           <t>https://www.remotecall.com/kr/use-cases/success-stories/technology/cresoty/</t>
         </is>
       </c>
-      <c r="D337" t="inlineStr"/>
-      <c r="E337" t="inlineStr"/>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -6174,8 +7052,11 @@
           <t>https://www.remotecall.com/kr/use-cases/success-stories/technology/cronyit</t>
         </is>
       </c>
-      <c r="D338" t="inlineStr"/>
-      <c r="E338" t="inlineStr"/>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -6191,8 +7072,11 @@
           <t>https://www.remotecall.com/kr/use-cases/success-stories/technology/cronyit/</t>
         </is>
       </c>
-      <c r="D339" t="inlineStr"/>
-      <c r="E339" t="inlineStr"/>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -6208,8 +7092,11 @@
           <t>https://www.remotecall.com/kr/use-cases/success-stories/technology/cudo-communication</t>
         </is>
       </c>
-      <c r="D340" t="inlineStr"/>
-      <c r="E340" t="inlineStr"/>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -6225,8 +7112,11 @@
           <t>https://www.remotecall.com/kr/use-cases/success-stories/technology/git</t>
         </is>
       </c>
-      <c r="D341" t="inlineStr"/>
-      <c r="E341" t="inlineStr"/>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -6242,8 +7132,11 @@
           <t>https://www.remotecall.com/kr/use-cases/success-stories/technology/goodmit</t>
         </is>
       </c>
-      <c r="D342" t="inlineStr"/>
-      <c r="E342" t="inlineStr"/>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -6259,8 +7152,11 @@
           <t>https://www.remotecall.com/kr/use-cases/success-stories/technology/greatcall</t>
         </is>
       </c>
-      <c r="D343" t="inlineStr"/>
-      <c r="E343" t="inlineStr"/>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -6276,8 +7172,11 @@
           <t>https://www.remotecall.com/kr/use-cases/success-stories/technology/greatcall/</t>
         </is>
       </c>
-      <c r="D344" t="inlineStr"/>
-      <c r="E344" t="inlineStr"/>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -6293,8 +7192,11 @@
           <t>https://www.remotecall.com/kr/use-cases/success-stories/technology/hauri</t>
         </is>
       </c>
-      <c r="D345" t="inlineStr"/>
-      <c r="E345" t="inlineStr"/>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -6310,8 +7212,11 @@
           <t>https://www.remotecall.com/kr/use-cases/success-stories/technology/ideait</t>
         </is>
       </c>
-      <c r="D346" t="inlineStr"/>
-      <c r="E346" t="inlineStr"/>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -6327,8 +7232,11 @@
           <t>https://www.remotecall.com/kr/use-cases/success-stories/technology/ideait/</t>
         </is>
       </c>
-      <c r="D347" t="inlineStr"/>
-      <c r="E347" t="inlineStr"/>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -6344,8 +7252,11 @@
           <t>https://www.remotecall.com/kr/use-cases/success-stories/technology/initech</t>
         </is>
       </c>
-      <c r="D348" t="inlineStr"/>
-      <c r="E348" t="inlineStr"/>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -6361,8 +7272,11 @@
           <t>https://www.remotecall.com/kr/use-cases/success-stories/technology/initech/</t>
         </is>
       </c>
-      <c r="D349" t="inlineStr"/>
-      <c r="E349" t="inlineStr"/>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -6378,8 +7292,11 @@
           <t>https://www.remotecall.com/kr/use-cases/success-stories/technology/jwonit</t>
         </is>
       </c>
-      <c r="D350" t="inlineStr"/>
-      <c r="E350" t="inlineStr"/>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -6395,8 +7312,11 @@
           <t>https://www.remotecall.com/kr/use-cases/success-stories/technology/jwonit/</t>
         </is>
       </c>
-      <c r="D351" t="inlineStr"/>
-      <c r="E351" t="inlineStr"/>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -6412,8 +7332,11 @@
           <t>https://www.remotecall.com/kr/use-cases/success-stories/technology/koiis</t>
         </is>
       </c>
-      <c r="D352" t="inlineStr"/>
-      <c r="E352" t="inlineStr"/>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -6429,8 +7352,11 @@
           <t>https://www.remotecall.com/kr/use-cases/success-stories/technology/koiis/</t>
         </is>
       </c>
-      <c r="D353" t="inlineStr"/>
-      <c r="E353" t="inlineStr"/>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -6446,8 +7372,11 @@
           <t>https://www.remotecall.com/kr/use-cases/success-stories/technology/ntt-docomo</t>
         </is>
       </c>
-      <c r="D354" t="inlineStr"/>
-      <c r="E354" t="inlineStr"/>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -6463,8 +7392,11 @@
           <t>https://www.remotecall.com/kr/use-cases/success-stories/technology/ntt-docomo/</t>
         </is>
       </c>
-      <c r="D355" t="inlineStr"/>
-      <c r="E355" t="inlineStr"/>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -6480,8 +7412,11 @@
           <t>https://www.remotecall.com/kr/use-cases/success-stories/technology/page/2/</t>
         </is>
       </c>
-      <c r="D356" t="inlineStr"/>
-      <c r="E356" t="inlineStr"/>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -6497,8 +7432,6 @@
           <t>https://www.remotecall.com/kr/use-cases/success-stories/technology/page/3/</t>
         </is>
       </c>
-      <c r="D357" t="inlineStr"/>
-      <c r="E357" t="inlineStr"/>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -6514,8 +7447,11 @@
           <t>https://www.remotecall.com/kr/use-cases/success-stories/technology/samil</t>
         </is>
       </c>
-      <c r="D358" t="inlineStr"/>
-      <c r="E358" t="inlineStr"/>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -6531,8 +7467,11 @@
           <t>https://www.remotecall.com/kr/use-cases/success-stories/technology/samil/</t>
         </is>
       </c>
-      <c r="D359" t="inlineStr"/>
-      <c r="E359" t="inlineStr"/>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -6548,8 +7487,11 @@
           <t>https://www.remotecall.com/kr/use-cases/success-stories/technology/tes-inc</t>
         </is>
       </c>
-      <c r="D360" t="inlineStr"/>
-      <c r="E360" t="inlineStr"/>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -6565,8 +7507,11 @@
           <t>https://www.remotecall.com/kr/use-cases/success-stories/technology/tes-inc/</t>
         </is>
       </c>
-      <c r="D361" t="inlineStr"/>
-      <c r="E361" t="inlineStr"/>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -6582,8 +7527,11 @@
           <t>https://www.remotecall.com/kr/use-cases/success-stories/technology/tocsg</t>
         </is>
       </c>
-      <c r="D362" t="inlineStr"/>
-      <c r="E362" t="inlineStr"/>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -6599,8 +7547,6 @@
           <t>(URL없음) RemoteCall-SaaS-Manual-Mobile-Support-Android-Ko.pdf</t>
         </is>
       </c>
-      <c r="D363" t="inlineStr"/>
-      <c r="E363" t="inlineStr"/>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -6616,8 +7562,6 @@
           <t>(URL없음) RemoteCall-SaaS-Manual-Mobile-Support-iOS-Ko.pdf</t>
         </is>
       </c>
-      <c r="D364" t="inlineStr"/>
-      <c r="E364" t="inlineStr"/>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -6633,8 +7577,11 @@
           <t>https://files.rsupport.com/ko/remotecall/guides/RemoteCall-SaaS-Manual-Mobile-Support-Android-Ko.pdf</t>
         </is>
       </c>
-      <c r="D365" t="inlineStr"/>
-      <c r="E365" t="inlineStr"/>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -6650,8 +7597,11 @@
           <t>https://files.rsupport.com/ko/remotecall/guides/RemoteCall-SaaS-Manual-Mobile-Support-iOS-Ko.pdf</t>
         </is>
       </c>
-      <c r="D366" t="inlineStr"/>
-      <c r="E366" t="inlineStr"/>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -6667,8 +7617,11 @@
           <t>https://files.rsupport.com/kr/remotecall/documents/user-guides/RemoteCall-Mobile-support-Android-guide-ko.pdf</t>
         </is>
       </c>
-      <c r="D367" t="inlineStr"/>
-      <c r="E367" t="inlineStr"/>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
@@ -6684,8 +7637,11 @@
           <t>https://files.rsupport.com/kr/remotecall/documents/user-guides/RemoteCall-Mobile-support-iOS-guide-ko.pdf</t>
         </is>
       </c>
-      <c r="D368" t="inlineStr"/>
-      <c r="E368" t="inlineStr"/>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -6701,8 +7657,6 @@
           <t>(URL없음) RemoteCall-SaaS-Manual-Visual-Support-Ko.pdf</t>
         </is>
       </c>
-      <c r="D369" t="inlineStr"/>
-      <c r="E369" t="inlineStr"/>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
@@ -6718,8 +7672,11 @@
           <t>https://files.rsupport.com/ko/remotecall/guides/RemoteCall-SaaS-Manual-Visual-Support-Ko.pdf</t>
         </is>
       </c>
-      <c r="D370" t="inlineStr"/>
-      <c r="E370" t="inlineStr"/>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
@@ -6735,8 +7692,11 @@
           <t>https://files.rsupport.com/kr/remotecall/documents/user-guides/RemoteCall-Visual-support-guide-ko.pdf</t>
         </is>
       </c>
-      <c r="D371" t="inlineStr"/>
-      <c r="E371" t="inlineStr"/>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
@@ -6752,8 +7712,6 @@
           <t>(URL없음) RemoteCall-SaaS-Agent-Manual-PC-Support-Ko.pdf</t>
         </is>
       </c>
-      <c r="D372" t="inlineStr"/>
-      <c r="E372" t="inlineStr"/>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
@@ -6769,8 +7727,11 @@
           <t>https://files.rsupport.com/ko/remotecall/guides/RemoteCall-SaaS-Agent-Manual-PC-Support-Ko.pdf</t>
         </is>
       </c>
-      <c r="D373" t="inlineStr"/>
-      <c r="E373" t="inlineStr"/>
+      <c r="E373" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
@@ -6786,8 +7747,11 @@
           <t>https://files.rsupport.com/kr/remotecall/documents/user-guides/RemoteCall-agent-PC-support-guide-ko.pdf</t>
         </is>
       </c>
-      <c r="D374" t="inlineStr"/>
-      <c r="E374" t="inlineStr"/>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -6803,8 +7767,6 @@
           <t>(URL없음) RemoteCall-SaaS-Manual-PC-Support-Ko.pdf</t>
         </is>
       </c>
-      <c r="D375" t="inlineStr"/>
-      <c r="E375" t="inlineStr"/>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
@@ -6820,8 +7782,11 @@
           <t>https://files.rsupport.com/ko/remotecall/guides/RemoteCall-SaaS-Manual-PC-Support-Ko.pdf</t>
         </is>
       </c>
-      <c r="D376" t="inlineStr"/>
-      <c r="E376" t="inlineStr"/>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -6837,8 +7802,11 @@
           <t>https://files.rsupport.com/kr/remotecall/documents/user-guides/RemoteCall-PC-support-guide-ko.pdf</t>
         </is>
       </c>
-      <c r="D377" t="inlineStr"/>
-      <c r="E377" t="inlineStr"/>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
@@ -6854,8 +7822,11 @@
           <t>https://www.remotecall.com/kr/trial/</t>
         </is>
       </c>
-      <c r="D378" t="inlineStr"/>
-      <c r="E378" t="inlineStr"/>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -6871,8 +7842,11 @@
           <t>https://www.remotecall.com/kr/trial/?utm_source=rsupblog&amp;utm_medium=referral&amp;utm_campaign=rcko-rsupport-naverblog</t>
         </is>
       </c>
-      <c r="D379" t="inlineStr"/>
-      <c r="E379" t="inlineStr"/>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -6888,8 +7862,11 @@
           <t>https://www.remotecall.com/kr/trial/re-trial/</t>
         </is>
       </c>
-      <c r="D380" t="inlineStr"/>
-      <c r="E380" t="inlineStr"/>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
@@ -6905,8 +7882,6 @@
           <t>(URL없음) RemoteCall-SaaS-Agent-Manual-Mobile-Support-Android-Ko.pdf</t>
         </is>
       </c>
-      <c r="D381" t="inlineStr"/>
-      <c r="E381" t="inlineStr"/>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
@@ -6922,8 +7897,11 @@
           <t>https://files.rsupport.com/ko/remotecall/guides/RemoteCall-SaaS-Agent-Manual-Mobile-Support-Android-Ko.pdf</t>
         </is>
       </c>
-      <c r="D382" t="inlineStr"/>
-      <c r="E382" t="inlineStr"/>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
@@ -6939,8 +7917,6 @@
           <t>(URL없음) RemoteCall-SaaS-User-Admin-Manual-Ko.pdf</t>
         </is>
       </c>
-      <c r="D383" t="inlineStr"/>
-      <c r="E383" t="inlineStr"/>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
@@ -6956,8 +7932,11 @@
           <t>https://files.rsupport.com/ko/remotecall/guides/RemoteCall-SaaS-User-Admin-Manual-Ko.pdf</t>
         </is>
       </c>
-      <c r="D384" t="inlineStr"/>
-      <c r="E384" t="inlineStr"/>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
@@ -6973,8 +7952,6 @@
           <t>(URL없음) RemoteCall-SaaS-Agent-Manual-Mobile-Support-iOS-Ko.pdf</t>
         </is>
       </c>
-      <c r="D385" t="inlineStr"/>
-      <c r="E385" t="inlineStr"/>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
@@ -6990,8 +7967,11 @@
           <t>https://files.rsupport.com/ko/remotecall/guides/RemoteCall-SaaS-Agent-Manual-Mobile-Support-iOS-Ko.pdf</t>
         </is>
       </c>
-      <c r="D386" t="inlineStr"/>
-      <c r="E386" t="inlineStr"/>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
@@ -7007,8 +7987,6 @@
           <t>(URL없음) RemoteCall-SaaS-Visual-Support-Quick-Guide-ko.pdf</t>
         </is>
       </c>
-      <c r="D387" t="inlineStr"/>
-      <c r="E387" t="inlineStr"/>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
@@ -7024,8 +8002,11 @@
           <t>https://files.rsupport.com/kr/remotecall/documents/user-guides/RemoteCall-SaaS-Visual-Support-Quick-Guide-ko.pdf</t>
         </is>
       </c>
-      <c r="D388" t="inlineStr"/>
-      <c r="E388" t="inlineStr"/>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
@@ -7041,8 +8022,6 @@
           <t>(URL없음) RemoteCall-product-specification-ko.pdf</t>
         </is>
       </c>
-      <c r="D389" t="inlineStr"/>
-      <c r="E389" t="inlineStr"/>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
@@ -7058,8 +8037,11 @@
           <t>https://files.rsupport.com/kr/remotecall/documents/features/RemoteCall-product-specification-ko.pdf</t>
         </is>
       </c>
-      <c r="D390" t="inlineStr"/>
-      <c r="E390" t="inlineStr"/>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
@@ -7075,8 +8057,6 @@
           <t>(URL없음) RemoteCall-Agent-Quick-Guide-ko.pdf</t>
         </is>
       </c>
-      <c r="D391" t="inlineStr"/>
-      <c r="E391" t="inlineStr"/>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
@@ -7092,8 +8072,11 @@
           <t>https://files.rsupport.com/kr/remotecall/documents/user-guides/RemoteCall-Agent-Quick-Guide-ko.pdf</t>
         </is>
       </c>
-      <c r="D392" t="inlineStr"/>
-      <c r="E392" t="inlineStr"/>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
@@ -7109,8 +8092,6 @@
           <t>(URL없음) RemoteCall-SaaS-Mobile-Support-iOS-Quick-Guide-ko.pdf</t>
         </is>
       </c>
-      <c r="D393" t="inlineStr"/>
-      <c r="E393" t="inlineStr"/>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
@@ -7126,8 +8107,11 @@
           <t>https://files.rsupport.com/kr/remotecall/documents/user-guides/RemoteCall-SaaS-Mobile-Support-iOS-Quick-Guide-ko.pdf</t>
         </is>
       </c>
-      <c r="D394" t="inlineStr"/>
-      <c r="E394" t="inlineStr"/>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
@@ -7143,8 +8127,6 @@
           <t>(URL없음) RemoteCall-SaaS-Agent-Manual-Visual-Support-Ko.pdf</t>
         </is>
       </c>
-      <c r="D395" t="inlineStr"/>
-      <c r="E395" t="inlineStr"/>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
@@ -7160,8 +8142,11 @@
           <t>https://files.rsupport.com/ko/remotecall/guides/RemoteCall-SaaS-Agent-Manual-Visual-Support-Ko.pdf</t>
         </is>
       </c>
-      <c r="D396" t="inlineStr"/>
-      <c r="E396" t="inlineStr"/>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
@@ -7177,8 +8162,6 @@
           <t>(URL없음) RemoteCall-SaaS-Mobile-Support-Android-Quick-Guide-ko.pdf</t>
         </is>
       </c>
-      <c r="D397" t="inlineStr"/>
-      <c r="E397" t="inlineStr"/>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
@@ -7194,8 +8177,11 @@
           <t>https://files.rsupport.com/kr/remotecall/documents/user-guides/RemoteCall-SaaS-Mobile-Support-Android-Quick-Guide-ko.pdf</t>
         </is>
       </c>
-      <c r="D398" t="inlineStr"/>
-      <c r="E398" t="inlineStr"/>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
@@ -7211,8 +8197,6 @@
           <t>(URL없음) RemoteCall-SaaS-PC-Support-Quick-Guide-ko.pdf</t>
         </is>
       </c>
-      <c r="D399" t="inlineStr"/>
-      <c r="E399" t="inlineStr"/>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
@@ -7228,8 +8212,11 @@
           <t>https://files.rsupport.com/kr/remotecall/documents/user-guides/RemoteCall-SaaS-PC-Support-Quick-Guide-ko.pdf</t>
         </is>
       </c>
-      <c r="D400" t="inlineStr"/>
-      <c r="E400" t="inlineStr"/>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
@@ -7245,8 +8232,6 @@
           <t>(URL없음) RemoteCall-Admin-Quick-Guide-ko.pdf</t>
         </is>
       </c>
-      <c r="D401" t="inlineStr"/>
-      <c r="E401" t="inlineStr"/>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
@@ -7262,8 +8247,11 @@
           <t>https://files.rsupport.com/kr/remotecall/documents/user-guides/RemoteCall-Admin-Quick-Guide-ko.pdf</t>
         </is>
       </c>
-      <c r="D402" t="inlineStr"/>
-      <c r="E402" t="inlineStr"/>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
@@ -7279,8 +8267,6 @@
           <t>(URL없음) RemoteCall-WebViewer-SDK-Intergration-Guide-Ko.pdf</t>
         </is>
       </c>
-      <c r="D403" t="inlineStr"/>
-      <c r="E403" t="inlineStr"/>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
@@ -7296,8 +8282,11 @@
           <t>https://files.rsupport.com/ko/remotecall/guides/RemoteCall-WebViewer-SDK-Intergration-Guide-Ko.pdf</t>
         </is>
       </c>
-      <c r="D404" t="inlineStr"/>
-      <c r="E404" t="inlineStr"/>
+      <c r="E404" t="inlineStr">
+        <is>
+          <t>⚠ 골든셋 정답 문서 — 보존 필수 (제거 시 해당 문항 무효)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7339,7 +8328,6 @@
           <t>RemoteCall-Admin-Quick-Guide-ko.pdf</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
           <t>PDF류 — 제목·URL·버전 메타 필수 (현재 참조 불가)</t>
@@ -7352,7 +8340,6 @@
           <t>RemoteCall-Agent-Quick-Guide-ko.pdf</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
           <t>PDF류 — 제목·URL·버전 메타 필수 (현재 참조 불가)</t>
@@ -7365,7 +8352,6 @@
           <t>RemoteCall-SaaS-Agent-Manual-Mobile-Support-Android-Ko.pdf</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
           <t>PDF류 — 제목·URL·버전 메타 필수 (현재 참조 불가)</t>
@@ -7378,7 +8364,6 @@
           <t>RemoteCall-SaaS-Agent-Manual-Mobile-Support-iOS-Ko.pdf</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>PDF류 — 제목·URL·버전 메타 필수 (현재 참조 불가)</t>
@@ -7391,7 +8376,6 @@
           <t>RemoteCall-SaaS-Agent-Manual-PC-Support-Ko.pdf</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>PDF류 — 제목·URL·버전 메타 필수 (현재 참조 불가)</t>
@@ -7404,7 +8388,6 @@
           <t>RemoteCall-SaaS-Agent-Manual-Visual-Support-Ko.pdf</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>PDF류 — 제목·URL·버전 메타 필수 (현재 참조 불가)</t>
@@ -7417,7 +8400,6 @@
           <t>RemoteCall-SaaS-Manual-Mobile-Support-Android-Ko.pdf</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
           <t>PDF류 — 제목·URL·버전 메타 필수 (현재 참조 불가)</t>
@@ -7430,7 +8412,6 @@
           <t>RemoteCall-SaaS-Manual-Mobile-Support-iOS-Ko.pdf</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
           <t>PDF류 — 제목·URL·버전 메타 필수 (현재 참조 불가)</t>
@@ -7443,7 +8424,6 @@
           <t>RemoteCall-SaaS-Manual-PC-Support-Ko.pdf</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
           <t>PDF류 — 제목·URL·버전 메타 필수 (현재 참조 불가)</t>
@@ -7456,7 +8436,6 @@
           <t>RemoteCall-SaaS-Manual-Visual-Support-Ko.pdf</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
           <t>PDF류 — 제목·URL·버전 메타 필수 (현재 참조 불가)</t>
@@ -7469,7 +8448,6 @@
           <t>RemoteCall-SaaS-Mobile-Support-Android-Quick-Guide-ko.pdf</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
           <t>PDF류 — 제목·URL·버전 메타 필수 (현재 참조 불가)</t>
@@ -7482,7 +8460,6 @@
           <t>RemoteCall-SaaS-Mobile-Support-iOS-Quick-Guide-ko.pdf</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
           <t>PDF류 — 제목·URL·버전 메타 필수 (현재 참조 불가)</t>
@@ -7495,7 +8472,6 @@
           <t>RemoteCall-SaaS-PC-Support-Quick-Guide-ko.pdf</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
           <t>PDF류 — 제목·URL·버전 메타 필수 (현재 참조 불가)</t>
@@ -7508,7 +8484,6 @@
           <t>RemoteCall-SaaS-User-Admin-Manual-Ko.pdf</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
           <t>PDF류 — 제목·URL·버전 메타 필수 (현재 참조 불가)</t>
@@ -7521,7 +8496,6 @@
           <t>RemoteCall-SaaS-Visual-Support-Quick-Guide-ko.pdf</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
           <t>PDF류 — 제목·URL·버전 메타 필수 (현재 참조 불가)</t>
@@ -7534,7 +8508,6 @@
           <t>RemoteCall-WebViewer-SDK-Intergration-Guide-Ko.pdf</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
           <t>PDF류 — 제목·URL·버전 메타 필수 (현재 참조 불가)</t>
@@ -7547,7 +8520,6 @@
           <t>RemoteCall-product-specification-ko.pdf</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
           <t>PDF류 — 제목·URL·버전 메타 필수 (현재 참조 불가)</t>
@@ -7560,7 +8532,6 @@
           <t>[RemoteCall 7.0] Known Issue_Spec List_ New (7.6.4~).xlsx</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
           <t>PDF류 — 제목·URL·버전 메타 필수 (현재 참조 불가)</t>
@@ -7573,7 +8544,6 @@
           <t>[RemoteCall 7.0] Products Specification_v1.7.xlsx</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
           <t>PDF류 — 제목·URL·버전 메타 필수 (현재 참조 불가)</t>
